--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95A615-D268-4F7A-84FF-694021F1ADE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80079B6-147F-4019-8A3C-DB46FCEA998C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
     <sheet name="ExtTest40mm_2" sheetId="2" r:id="rId2"/>
-    <sheet name="ExtTest20mm_1" sheetId="3" r:id="rId3"/>
-    <sheet name="FlxTest20mm_42cm" sheetId="4" r:id="rId4"/>
-    <sheet name="FlxTest20mm_39cm" sheetId="5" r:id="rId5"/>
-    <sheet name="FlxTest20mm_39cm (2)" sheetId="6" r:id="rId6"/>
-    <sheet name="FlxTest20mm_42cm (2)" sheetId="7" r:id="rId7"/>
-    <sheet name="FlxTest20mm_42cm (3)" sheetId="8" r:id="rId8"/>
-    <sheet name="FlxTest20mm_51cm" sheetId="9" r:id="rId9"/>
+    <sheet name="ExtTest20mm_1" sheetId="10" r:id="rId3"/>
+    <sheet name="ExtTest20mm_2" sheetId="3" r:id="rId4"/>
+    <sheet name="FlxTest20mm_42cm" sheetId="4" r:id="rId5"/>
+    <sheet name="FlxTest20mm_39cm" sheetId="5" r:id="rId6"/>
+    <sheet name="FlxTest20mm_39cm (2)" sheetId="6" r:id="rId7"/>
+    <sheet name="FlxTest20mm_42cm (2)" sheetId="7" r:id="rId8"/>
+    <sheet name="FlxTest20mm_42cm (3)" sheetId="8" r:id="rId9"/>
+    <sheet name="FlxTest20mm_51cm" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="59">
   <si>
     <t>Flexor Test 20mm</t>
   </si>
@@ -503,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -541,11 +542,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1025,7 +1025,14 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1165,7 +1172,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FE37-4FC1-8A2D-AAA215DD1B14}"/>
+              <c16:uniqueId val="{00000000-70CA-4C5B-BA43-A58DAB21265A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1235,166 +1242,134 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>20 mm Flexor Torque</a:t>
+              <a:t>20 mm Extensor Torque</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
+      <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>500 kPA</c:v>
-          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="7"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.11194116360454941"/>
-                  <c:y val="0.27785177894429858"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest20mm_42cm!$M$7:$Q$7</c:f>
+              <c:f>ExtTest20mm_2!$C$7:$X$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>-73.5</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-82</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-88</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-103.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-114</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest20mm_42cm!$M$16:$Q$16</c:f>
+              <c:f>ExtTest20mm_2!$C$16:$X$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>-5.6806977708149313</c:v>
+                  <c:v>1.0381838898090796</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4.0392598352753879</c:v>
+                  <c:v>6.9717875622415679</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-3.2513783399694391</c:v>
+                  <c:v>20.758112821237887</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.3263579017259233</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.70598947320621186</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1402,279 +1377,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-499C-4AD7-BEC4-086D0D7C5493}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>300 kPa</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>FlxTest20mm_42cm!$C$7:$L$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-11.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-27</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-35</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-44</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-54.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-50</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-63</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-64</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>FlxTest20mm_42cm!$C$16:$L$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>-9.9520752292838743</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-8.309776190397633</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-6.9372085405748338</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-5.8312110803111104</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-4.6528169082585853</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-3.5943174716264252</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-3.5754544525113139</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-3.0265514767141273</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-2.199767728579054</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-0.92210333898321939</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-499C-4AD7-BEC4-086D0D7C5493}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>620 kPa</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="5.8333333333333327E-2"/>
-                  <c:y val="0.37889690871974341"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>FlxTest20mm_42cm!$R$7:$S$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-115</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-120</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>FlxTest20mm_42cm!$R$16:$S$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-1.826208161538696</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1.0937153129886135</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-499C-4AD7-BEC4-086D0D7C5493}"/>
+              <c16:uniqueId val="{00000000-FE37-4FC1-8A2D-AAA215DD1B14}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1686,130 +1389,38 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1221401968"/>
-        <c:axId val="1221403632"/>
+        <c:axId val="10"/>
+        <c:axId val="20"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1221401968"/>
+        <c:axId val="10"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1221403632"/>
+        <c:crossAx val="20"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1221403632"/>
+        <c:axId val="20"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1221401968"/>
+        <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1818,21 +1429,6 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1969,33 +1565,48 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$M$7:$Q$7</c:f>
+              <c:f>FlxTest20mm_42cm!$M$7:$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-73.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-88</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-103.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$M$16:$Q$16</c:f>
+              <c:f>FlxTest20mm_42cm!$M$16:$Q$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-5.6806977708149313</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-4.0392598352753879</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-3.2513783399694391</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>-1.3263579017259233</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>-0.70598947320621186</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2003,7 +1614,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FBE6-4771-8BEB-270FED64EA26}"/>
+              <c16:uniqueId val="{00000001-499C-4AD7-BEC4-086D0D7C5493}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2046,34 +1657,73 @@
             </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="2"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$C$7:$L$7</c:f>
+              <c:f>FlxTest20mm_42cm!$C$7:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-124</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-98.5</c:v>
+                  <c:v>-11.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-118.5</c:v>
+                  <c:v>-20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-111</c:v>
+                  <c:v>-27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-90</c:v>
+                  <c:v>-35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-75</c:v>
+                  <c:v>-44</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>-54.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>-64</c:v>
                 </c:pt>
               </c:numCache>
@@ -2081,39 +1731,39 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$C$16:$L$16</c:f>
+              <c:f>FlxTest20mm_42cm!$C$16:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-5.6541833371388703</c:v>
+                  <c:v>-9.9520752292838743</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-11.416082319316914</c:v>
+                  <c:v>-8.309776190397633</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.7080411596584568</c:v>
+                  <c:v>-6.9372085405748338</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10.218147814891781</c:v>
+                  <c:v>-5.8312110803111104</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13.937767935473495</c:v>
+                  <c:v>-4.6528169082585853</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-17.298116513358377</c:v>
+                  <c:v>-3.5943174716264252</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-20.398495906594288</c:v>
+                  <c:v>-3.5754544525113139</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>-3.0265514767141273</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-2.199767728579054</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>-0.92210333898321939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2121,7 +1771,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-FBE6-4771-8BEB-270FED64EA26}"/>
+              <c16:uniqueId val="{00000003-499C-4AD7-BEC4-086D0D7C5493}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2205,24 +1855,30 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$R$7:$S$7</c:f>
+              <c:f>FlxTest20mm_42cm!$R$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>-115</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest20mm_39cm!$R$16:$S$16</c:f>
+              <c:f>FlxTest20mm_42cm!$R$16:$S$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-1.826208161538696</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-1.0937153129886135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2230,7 +1886,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-FBE6-4771-8BEB-270FED64EA26}"/>
+              <c16:uniqueId val="{00000005-499C-4AD7-BEC4-086D0D7C5493}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2525,7 +2181,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$M$7:$Q$7</c:f>
+              <c:f>FlxTest20mm_39cm!$M$7:$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2534,7 +2190,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$M$16:$Q$16</c:f>
+              <c:f>FlxTest20mm_39cm!$M$16:$Q$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2559,7 +2215,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3397-422A-9758-957B933614E7}"/>
+              <c16:uniqueId val="{00000001-FBE6-4771-8BEB-270FED64EA26}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2607,51 +2263,60 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$C$7:$L$7</c:f>
+              <c:f>FlxTest20mm_39cm!$C$7:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-125</c:v>
+                  <c:v>-124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-112</c:v>
+                  <c:v>-98.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-91.5</c:v>
+                  <c:v>-118.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-111</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-90</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$C$16:$L$16</c:f>
+              <c:f>FlxTest20mm_39cm!$C$16:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-3.2074362177995286</c:v>
+                  <c:v>-5.6541833371388703</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-8.7827488537996867</c:v>
+                  <c:v>-11.416082319316914</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-11.489901909669882</c:v>
+                  <c:v>-5.7080411596584568</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-16.172026211620985</c:v>
+                  <c:v>-10.218147814891781</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>-13.937767935473495</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>-17.298116513358377</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>-20.398495906594288</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -2668,7 +2333,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3397-422A-9758-957B933614E7}"/>
+              <c16:uniqueId val="{00000003-FBE6-4771-8BEB-270FED64EA26}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2752,7 +2417,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$R$7:$S$7</c:f>
+              <c:f>FlxTest20mm_39cm!$R$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2761,7 +2426,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_39cm (2)'!$R$16:$S$16</c:f>
+              <c:f>FlxTest20mm_39cm!$R$16:$S$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2777,7 +2442,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-3397-422A-9758-957B933614E7}"/>
+              <c16:uniqueId val="{00000005-FBE6-4771-8BEB-270FED64EA26}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3072,7 +2737,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$M$7:$Q$7</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$M$7:$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3081,7 +2746,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$M$16:$Q$16</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$M$16:$Q$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3106,7 +2771,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9521-4D9A-B379-377146290C08}"/>
+              <c16:uniqueId val="{00000001-3397-422A-9758-957B933614E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3154,7 +2819,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$C$7:$L$7</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$C$7:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3165,55 +2830,43 @@
                   <c:v>-112</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-93</c:v>
+                  <c:v>-91.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-80</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>-75</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-52</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-42</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$C$16:$L$16</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$C$16:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-1.5702056777668703</c:v>
+                  <c:v>-3.2074362177995286</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.0305367147524738</c:v>
+                  <c:v>-8.7827488537996867</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.049415693445349</c:v>
+                  <c:v>-11.489901909669882</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-14.462104379205506</c:v>
+                  <c:v>-16.172026211620985</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-18.54620852024544</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-22.519923786080557</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-25.525501816571964</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-26.999475495745692</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3227,7 +2880,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-9521-4D9A-B379-377146290C08}"/>
+              <c16:uniqueId val="{00000003-3397-422A-9758-957B933614E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +2964,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$R$7:$S$7</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$R$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3320,7 +2973,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (2)'!$R$16:$S$16</c:f>
+              <c:f>'FlxTest20mm_39cm (2)'!$R$16:$S$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3336,7 +2989,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-9521-4D9A-B379-377146290C08}"/>
+              <c16:uniqueId val="{00000005-3397-422A-9758-957B933614E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3554,6 +3207,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>500 kPA</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:noFill/>
@@ -3576,103 +3232,84 @@
               </a:ln>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.11194116360454941"/>
+                  <c:y val="0.27785177894429858"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$N$7:$AD$7</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$M$7:$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>-26.01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-26.001000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-18.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-7</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.7</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-6.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-32</c:v>
-                </c:pt>
+                <c:ptCount val="5"/>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$N$16:$AD$16</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$M$16:$Q$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-19.227454254339136</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-22.870810329712633</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-15.303755097401908</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-23.614928776430023</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-16.964330062819261</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-20.512556348769913</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-22.524669621589222</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-22.445422242164838</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-24.683174896031996</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-31.305765433684865</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-24.076391978101967</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3681,13 +3318,16 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+              <c16:uniqueId val="{00000001-9521-4D9A-B379-377146290C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>300 kPa</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -3726,84 +3366,72 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$C$7:$M$7</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$C$7:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>-125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-114</c:v>
+                  <c:v>-112</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-98</c:v>
+                  <c:v>-93</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-83</c:v>
+                  <c:v>-80</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-75.5</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-69</c:v>
+                  <c:v>-52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-55.5</c:v>
+                  <c:v>-42</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-53.000999999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-53.01</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-41</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-30</c:v>
+                  <c:v>-32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$C$16:$M$16</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$C$16:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-5.6260680394816323</c:v>
+                  <c:v>-1.5702056777668703</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-5.620399172616299</c:v>
+                  <c:v>-6.0305367147524738</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.136558498526179</c:v>
+                  <c:v>-10.049415693445349</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.182897163275499</c:v>
+                  <c:v>-14.462104379205506</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.441726709946776</c:v>
+                  <c:v>-18.54620852024544</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-17.25259369975322</c:v>
+                  <c:v>-22.519923786080557</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-20.883378186341204</c:v>
+                  <c:v>-25.525501816571964</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-22.6507412457938</c:v>
+                  <c:v>-26.999475495745692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-23.16548730865841</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-28.66833854611783</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-31.996455925810519</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3811,7 +3439,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+              <c16:uniqueId val="{00000003-9521-4D9A-B379-377146290C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3854,35 +3482,65 @@
             </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="2"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="5.8333333333333327E-2"/>
+                  <c:y val="0.37889690871974341"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$R$7:$S$7</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$R$7:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-7</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-9</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'FlxTest20mm_42cm (3)'!$R$16:$S$16</c:f>
+              <c:f>'FlxTest20mm_42cm (2)'!$R$16:$S$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>-16.964330062819261</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-20.512556348769913</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3890,7 +3548,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+              <c16:uniqueId val="{00000005-9521-4D9A-B379-377146290C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4067,6 +3725,560 @@
     <c:title>
       <c:tx>
         <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>20 mm Flexor Torque</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$N$7:$AD$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>-26.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-26.001000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-18.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$N$16:$AD$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>-19.227454254339136</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-22.870810329712633</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-15.303755097401908</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-23.614928776430023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-16.964330062819261</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-20.512556348769913</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-22.524669621589222</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-22.445422242164838</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-24.683174896031996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-31.305765433684865</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-24.076391978101967</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$C$7:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-114</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-75.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-55.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-53.000999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-53.01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-41</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$C$16:$M$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-5.6260680394816323</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.620399172616299</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-10.136558498526179</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-13.182897163275499</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-14.441726709946776</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-17.25259369975322</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-20.883378186341204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-22.6507412457938</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-23.16548730865841</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-28.66833854611783</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-31.996455925810519</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>620 kPa</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$R$7:$S$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'FlxTest20mm_42cm (3)'!$R$16:$S$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>-16.964330062819261</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-20.512556348769913</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-EA9E-4B1B-8BF0-F2CB549190B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1221401968"/>
+        <c:axId val="1221403632"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1221401968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1221403632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1221403632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1221401968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
@@ -4314,6 +4526,49 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5EC0F2-1CA3-47DE-813F-F23689B236C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
@@ -4335,7 +4590,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4376,7 +4631,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4417,7 +4672,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4458,7 +4713,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4499,7 +4754,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4540,7 +4795,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5611,448 +5866,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>462.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>84.117999999999995</v>
-      </c>
-      <c r="D6">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>604</v>
-      </c>
-      <c r="D8">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>14.6</v>
-      </c>
-      <c r="D10">
-        <v>14.6</v>
-      </c>
-      <c r="E10">
-        <v>14.6</v>
-      </c>
-      <c r="F10">
-        <v>14.6</v>
-      </c>
-      <c r="G10">
-        <v>14.6</v>
-      </c>
-      <c r="H10">
-        <v>14.6</v>
-      </c>
-      <c r="I10">
-        <v>14.6</v>
-      </c>
-      <c r="J10">
-        <v>14.6</v>
-      </c>
-      <c r="K10">
-        <v>14.6</v>
-      </c>
-      <c r="L10">
-        <v>14.6</v>
-      </c>
-      <c r="M10">
-        <v>14.6</v>
-      </c>
-      <c r="N10">
-        <v>14.6</v>
-      </c>
-      <c r="O10">
-        <v>14.6</v>
-      </c>
-      <c r="P10">
-        <v>14.6</v>
-      </c>
-      <c r="Q10">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12">
-        <f>($C$2-C11)/$C$2</f>
-        <v>0.28366247755834828</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14">
-        <v>240.61</v>
-      </c>
-      <c r="D14">
-        <v>240.61</v>
-      </c>
-      <c r="E14">
-        <v>240.61</v>
-      </c>
-      <c r="F14">
-        <v>240.61</v>
-      </c>
-      <c r="G14">
-        <v>240.61</v>
-      </c>
-      <c r="H14">
-        <v>240.61</v>
-      </c>
-      <c r="I14">
-        <v>240.61</v>
-      </c>
-      <c r="J14">
-        <v>240.61</v>
-      </c>
-      <c r="K14">
-        <v>240.61</v>
-      </c>
-      <c r="L14">
-        <v>240.61</v>
-      </c>
-      <c r="M14">
-        <v>240.61</v>
-      </c>
-      <c r="N14">
-        <v>240.61</v>
-      </c>
-      <c r="O14">
-        <v>240.61</v>
-      </c>
-      <c r="P14">
-        <v>240.61</v>
-      </c>
-      <c r="Q14">
-        <v>240.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <f>C6*COS(RADIANS(C10-4.2))*C14/1000</f>
-        <v>19.907124595290242</v>
-      </c>
-      <c r="D17">
-        <f>D6*COS(RADIANS(D10-5))*D14/1000</f>
-        <v>29.41782280346224</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ref="E17:Q17" si="0">E6*COS(RADIANS(E10))*E14/1000</f>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18">
-        <v>30.556999999999999</v>
-      </c>
-      <c r="D18">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22">
-        <v>18.260899999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C23">
-        <v>2.018E-2</v>
-      </c>
-      <c r="D23">
-        <v>-0.11126999999999999</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="C27">
-        <v>3.619E-2</v>
-      </c>
-      <c r="D27">
-        <v>-6.3950000000000007E-2</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6068,25 +5883,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -6098,22 +5895,19 @@
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
         <v>7</v>
       </c>
@@ -6188,15 +5982,9 @@
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="36">
-        <v>3.7</v>
-      </c>
-      <c r="D6" s="36">
-        <v>25.2</v>
-      </c>
-      <c r="E6" s="36">
-        <v>76</v>
-      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -6221,15 +6009,9 @@
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="37">
-        <v>10</v>
-      </c>
-      <c r="D7" s="37">
-        <v>11</v>
-      </c>
-      <c r="E7" s="37">
-        <v>10</v>
-      </c>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
@@ -6254,15 +6036,9 @@
       <c r="B8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="38">
-        <v>388.5</v>
-      </c>
-      <c r="D8" s="38">
-        <v>388</v>
-      </c>
-      <c r="E8" s="38">
-        <v>592</v>
-      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="38"/>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
@@ -6317,15 +6093,9 @@
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37">
-        <v>72.5</v>
-      </c>
-      <c r="D10" s="37">
-        <v>70</v>
-      </c>
-      <c r="E10" s="37">
-        <v>68</v>
-      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
       <c r="F10" s="37"/>
       <c r="G10" s="37"/>
       <c r="H10" s="37"/>
@@ -6407,72 +6177,28 @@
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="D13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="E13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="F13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="G13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="H13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="I13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="J13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="K13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="L13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="M13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="N13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="O13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="P13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="Q13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="R13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="S13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="T13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="U13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="V13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="W13" s="37">
-        <v>292.89999999999998</v>
-      </c>
-      <c r="X13" s="37">
-        <v>292.89999999999998</v>
-      </c>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
@@ -6529,7 +6255,1058 @@
       <c r="X15" s="38"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="36">
+        <f t="shared" ref="C16:X16" si="0">-C6*COS(RADIANS(C10-2.83))*C13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="36"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="36"/>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>462.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>84.117999999999995</v>
+      </c>
+      <c r="D6">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>604</v>
+      </c>
+      <c r="D8">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>14.6</v>
+      </c>
+      <c r="D10">
+        <v>14.6</v>
+      </c>
+      <c r="E10">
+        <v>14.6</v>
+      </c>
+      <c r="F10">
+        <v>14.6</v>
+      </c>
+      <c r="G10">
+        <v>14.6</v>
+      </c>
+      <c r="H10">
+        <v>14.6</v>
+      </c>
+      <c r="I10">
+        <v>14.6</v>
+      </c>
+      <c r="J10">
+        <v>14.6</v>
+      </c>
+      <c r="K10">
+        <v>14.6</v>
+      </c>
+      <c r="L10">
+        <v>14.6</v>
+      </c>
+      <c r="M10">
+        <v>14.6</v>
+      </c>
+      <c r="N10">
+        <v>14.6</v>
+      </c>
+      <c r="O10">
+        <v>14.6</v>
+      </c>
+      <c r="P10">
+        <v>14.6</v>
+      </c>
+      <c r="Q10">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12">
+        <f>($C$2-C11)/$C$2</f>
+        <v>0.28366247755834828</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>240.61</v>
+      </c>
+      <c r="D14">
+        <v>240.61</v>
+      </c>
+      <c r="E14">
+        <v>240.61</v>
+      </c>
+      <c r="F14">
+        <v>240.61</v>
+      </c>
+      <c r="G14">
+        <v>240.61</v>
+      </c>
+      <c r="H14">
+        <v>240.61</v>
+      </c>
+      <c r="I14">
+        <v>240.61</v>
+      </c>
+      <c r="J14">
+        <v>240.61</v>
+      </c>
+      <c r="K14">
+        <v>240.61</v>
+      </c>
+      <c r="L14">
+        <v>240.61</v>
+      </c>
+      <c r="M14">
+        <v>240.61</v>
+      </c>
+      <c r="N14">
+        <v>240.61</v>
+      </c>
+      <c r="O14">
+        <v>240.61</v>
+      </c>
+      <c r="P14">
+        <v>240.61</v>
+      </c>
+      <c r="Q14">
+        <v>240.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <f>C6*COS(RADIANS(C10-4.2))*C14/1000</f>
+        <v>19.907124595290242</v>
+      </c>
+      <c r="D17">
+        <f>D6*COS(RADIANS(D10-5))*D14/1000</f>
+        <v>29.41782280346224</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:Q17" si="0">E6*COS(RADIANS(E10))*E14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>30.556999999999999</v>
+      </c>
+      <c r="D18">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22">
+        <v>18.260899999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>2.018E-2</v>
+      </c>
+      <c r="D23">
+        <v>-0.11126999999999999</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>3.619E-2</v>
+      </c>
+      <c r="D27">
+        <v>-6.3950000000000007E-2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{411EFBF4-5987-49CA-839E-BE22E507CBB9}">
+  <dimension ref="A1:X21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="35">
+        <v>1</v>
+      </c>
+      <c r="D5" s="35">
+        <v>2</v>
+      </c>
+      <c r="E5" s="35">
+        <v>3</v>
+      </c>
+      <c r="F5" s="35">
+        <v>4</v>
+      </c>
+      <c r="G5" s="35">
+        <v>5</v>
+      </c>
+      <c r="H5" s="35">
+        <v>6</v>
+      </c>
+      <c r="I5" s="35">
+        <v>7</v>
+      </c>
+      <c r="J5" s="35">
+        <v>8</v>
+      </c>
+      <c r="K5" s="35">
+        <v>9</v>
+      </c>
+      <c r="L5" s="35">
+        <v>10</v>
+      </c>
+      <c r="M5" s="35">
+        <v>11</v>
+      </c>
+      <c r="N5" s="35">
+        <v>12</v>
+      </c>
+      <c r="O5" s="35">
+        <v>13</v>
+      </c>
+      <c r="P5" s="35">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="35">
+        <v>15</v>
+      </c>
+      <c r="R5" s="35">
+        <v>16</v>
+      </c>
+      <c r="S5" s="35">
+        <v>17</v>
+      </c>
+      <c r="T5" s="35">
+        <v>18</v>
+      </c>
+      <c r="U5" s="35">
+        <v>19</v>
+      </c>
+      <c r="V5" s="35">
+        <v>20</v>
+      </c>
+      <c r="W5" s="35">
+        <v>21</v>
+      </c>
+      <c r="X5" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="36">
+        <v>3.7</v>
+      </c>
+      <c r="D6" s="36">
+        <v>25.2</v>
+      </c>
+      <c r="E6" s="36">
+        <v>76</v>
+      </c>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="37">
+        <v>10</v>
+      </c>
+      <c r="D7" s="37">
+        <v>11</v>
+      </c>
+      <c r="E7" s="37">
+        <v>10</v>
+      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+    </row>
+    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="38">
+        <v>388.5</v>
+      </c>
+      <c r="D8" s="38">
+        <v>388</v>
+      </c>
+      <c r="E8" s="38">
+        <v>592</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="37">
+        <v>72.5</v>
+      </c>
+      <c r="D10" s="37">
+        <v>70</v>
+      </c>
+      <c r="E10" s="37">
+        <v>68</v>
+      </c>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+    </row>
+    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="D13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="E13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="F13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="G13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="H13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="I13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="J13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="K13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="L13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="M13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="N13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="O13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="P13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="Q13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="R13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="S13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="T13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="U13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="V13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="W13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="X13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+    </row>
+    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="36">
@@ -6663,6 +7440,617 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:X21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="35">
+        <v>1</v>
+      </c>
+      <c r="D5" s="35">
+        <v>2</v>
+      </c>
+      <c r="E5" s="35">
+        <v>3</v>
+      </c>
+      <c r="F5" s="35">
+        <v>4</v>
+      </c>
+      <c r="G5" s="35">
+        <v>5</v>
+      </c>
+      <c r="H5" s="35">
+        <v>6</v>
+      </c>
+      <c r="I5" s="35">
+        <v>7</v>
+      </c>
+      <c r="J5" s="35">
+        <v>8</v>
+      </c>
+      <c r="K5" s="35">
+        <v>9</v>
+      </c>
+      <c r="L5" s="35">
+        <v>10</v>
+      </c>
+      <c r="M5" s="35">
+        <v>11</v>
+      </c>
+      <c r="N5" s="35">
+        <v>12</v>
+      </c>
+      <c r="O5" s="35">
+        <v>13</v>
+      </c>
+      <c r="P5" s="35">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="35">
+        <v>15</v>
+      </c>
+      <c r="R5" s="35">
+        <v>16</v>
+      </c>
+      <c r="S5" s="35">
+        <v>17</v>
+      </c>
+      <c r="T5" s="35">
+        <v>18</v>
+      </c>
+      <c r="U5" s="35">
+        <v>19</v>
+      </c>
+      <c r="V5" s="35">
+        <v>20</v>
+      </c>
+      <c r="W5" s="35">
+        <v>21</v>
+      </c>
+      <c r="X5" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="36">
+        <v>3.7</v>
+      </c>
+      <c r="D6" s="36">
+        <v>25.2</v>
+      </c>
+      <c r="E6" s="36">
+        <v>76</v>
+      </c>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="37">
+        <v>10</v>
+      </c>
+      <c r="D7" s="37">
+        <v>11</v>
+      </c>
+      <c r="E7" s="37">
+        <v>10</v>
+      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+    </row>
+    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="38">
+        <v>388.5</v>
+      </c>
+      <c r="D8" s="38">
+        <v>388</v>
+      </c>
+      <c r="E8" s="38">
+        <v>592</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="37">
+        <v>72.5</v>
+      </c>
+      <c r="D10" s="37">
+        <v>70</v>
+      </c>
+      <c r="E10" s="37">
+        <v>68</v>
+      </c>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+    </row>
+    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="D13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="E13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="F13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="G13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="H13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="I13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="J13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="K13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="L13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="M13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="N13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="O13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="P13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="Q13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="R13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="S13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="T13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="U13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="V13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="W13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+      <c r="X13" s="37">
+        <v>292.89999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+    </row>
+    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="36">
+        <f>C6*SIN(RADIANS(C10+0.83))*C13/1000</f>
+        <v>1.0381838898090796</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" ref="D16:X16" si="0">D6*SIN(RADIANS(D10+0.83))*D13/1000</f>
+        <v>6.9717875622415679</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="0"/>
+        <v>20.758112821237887</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7431,7 +8819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7913,7 +9301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8344,7 +9732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8850,7 +10238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AD21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9861,526 +11249,4 @@
   <pageSetup orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B5" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="35">
-        <v>1</v>
-      </c>
-      <c r="D5" s="35">
-        <v>2</v>
-      </c>
-      <c r="E5" s="35">
-        <v>3</v>
-      </c>
-      <c r="F5" s="35">
-        <v>4</v>
-      </c>
-      <c r="G5" s="35">
-        <v>5</v>
-      </c>
-      <c r="H5" s="35">
-        <v>6</v>
-      </c>
-      <c r="I5" s="35">
-        <v>7</v>
-      </c>
-      <c r="J5" s="35">
-        <v>8</v>
-      </c>
-      <c r="K5" s="35">
-        <v>9</v>
-      </c>
-      <c r="L5" s="35">
-        <v>10</v>
-      </c>
-      <c r="M5" s="35">
-        <v>11</v>
-      </c>
-      <c r="N5" s="35">
-        <v>12</v>
-      </c>
-      <c r="O5" s="35">
-        <v>13</v>
-      </c>
-      <c r="P5" s="35">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="35">
-        <v>15</v>
-      </c>
-      <c r="R5" s="35">
-        <v>16</v>
-      </c>
-      <c r="S5" s="35">
-        <v>17</v>
-      </c>
-      <c r="T5" s="35">
-        <v>18</v>
-      </c>
-      <c r="U5" s="35">
-        <v>19</v>
-      </c>
-      <c r="V5" s="35">
-        <v>20</v>
-      </c>
-      <c r="W5" s="35">
-        <v>21</v>
-      </c>
-      <c r="X5" s="35">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-    </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-    </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="37"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="37"/>
-      <c r="X14" s="37"/>
-    </row>
-    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="36">
-        <f t="shared" ref="C16:X16" si="0">-C6*COS(RADIANS(C10-2.83))*C13/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80079B6-147F-4019-8A3C-DB46FCEA998C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D541CE-E7A5-4DC6-B614-B6F65C853A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
     <sheet name="ExtTest40mm_2" sheetId="2" r:id="rId2"/>
     <sheet name="ExtTest20mm_1" sheetId="10" r:id="rId3"/>
-    <sheet name="ExtTest20mm_2" sheetId="3" r:id="rId4"/>
+    <sheet name="ExtTest20mm_2" sheetId="11" r:id="rId4"/>
     <sheet name="FlxTest20mm_42cm" sheetId="4" r:id="rId5"/>
     <sheet name="FlxTest20mm_39cm" sheetId="5" r:id="rId6"/>
     <sheet name="FlxTest20mm_39cm (2)" sheetId="6" r:id="rId7"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="60">
   <si>
     <t>Flexor Test 20mm</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Torque at t1</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1240,14 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1288,13 +1298,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>-26.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>-30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>-61</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-119</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1306,22 +1325,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>1.0381838898090796</c:v>
+                  <c:v>43.460736823868544</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.9717875622415679</c:v>
+                  <c:v>44.185666386660522</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.758112821237887</c:v>
+                  <c:v>41.376763734939175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>43.865492956682836</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>29.094426649018608</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>24.781100465532006</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -1377,7 +1396,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FE37-4FC1-8A2D-AAA215DD1B14}"/>
+              <c16:uniqueId val="{00000000-024E-4B50-9FEF-6C2014DD174B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4569,11 +4588,13 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A51F9805-328B-4D57-BA65-7B91B7B89C3E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7440,8 +7461,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2ABF78-C1E8-448F-AF95-D36F16313176}">
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -7577,17 +7598,23 @@
         <v>8</v>
       </c>
       <c r="C6" s="36">
-        <v>3.7</v>
+        <v>180.2</v>
       </c>
       <c r="D6" s="36">
-        <v>25.2</v>
+        <v>181.5</v>
       </c>
       <c r="E6" s="36">
-        <v>76</v>
-      </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+        <v>168</v>
+      </c>
+      <c r="F6" s="36">
+        <v>181</v>
+      </c>
+      <c r="G6" s="36">
+        <v>116</v>
+      </c>
+      <c r="H6" s="36">
+        <v>100</v>
+      </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36"/>
       <c r="K6" s="36"/>
@@ -7610,17 +7637,23 @@
         <v>9</v>
       </c>
       <c r="C7" s="37">
-        <v>10</v>
+        <v>-26.2</v>
       </c>
       <c r="D7" s="37">
-        <v>11</v>
+        <v>-30</v>
       </c>
       <c r="E7" s="37">
-        <v>10</v>
-      </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
+        <v>-61</v>
+      </c>
+      <c r="F7" s="37">
+        <v>-43</v>
+      </c>
+      <c r="G7" s="37">
+        <v>-119</v>
+      </c>
+      <c r="H7" s="37">
+        <v>5</v>
+      </c>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -7643,17 +7676,23 @@
         <v>10</v>
       </c>
       <c r="C8" s="38">
-        <v>388.5</v>
+        <v>437</v>
       </c>
       <c r="D8" s="38">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E8" s="38">
-        <v>592</v>
-      </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
+        <v>425</v>
+      </c>
+      <c r="F8" s="38">
+        <v>435</v>
+      </c>
+      <c r="G8" s="38">
+        <v>256</v>
+      </c>
+      <c r="H8" s="38">
+        <v>480</v>
+      </c>
       <c r="I8" s="38"/>
       <c r="J8" s="38"/>
       <c r="K8" s="38"/>
@@ -7706,17 +7745,23 @@
         <v>13</v>
       </c>
       <c r="C10" s="37">
-        <v>72.5</v>
+        <v>28</v>
       </c>
       <c r="D10" s="37">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E10" s="37">
-        <v>68</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
+        <v>23</v>
+      </c>
+      <c r="F10" s="37">
+        <v>27</v>
+      </c>
+      <c r="G10" s="37">
+        <v>10.5</v>
+      </c>
+      <c r="H10" s="37">
+        <v>21</v>
+      </c>
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
       <c r="K10" s="37"/>
@@ -7796,70 +7841,70 @@
         <v>17</v>
       </c>
       <c r="C13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="D13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="E13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="F13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="G13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="H13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="I13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="J13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="K13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="L13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="M13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="N13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="O13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="P13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="Q13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="R13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="S13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="T13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="U13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="V13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="W13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
       <c r="X13" s="37">
-        <v>292.89999999999998</v>
+        <v>250.9</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -7921,28 +7966,28 @@
         <v>58</v>
       </c>
       <c r="C16" s="36">
-        <f>C6*SIN(RADIANS(C10+0.83))*C13/1000</f>
-        <v>1.0381838898090796</v>
+        <f>C6*COS(RADIANS(C10-12))*C13/1000</f>
+        <v>43.460736823868544</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:X16" si="0">D6*SIN(RADIANS(D10+0.83))*D13/1000</f>
-        <v>6.9717875622415679</v>
+        <f t="shared" ref="D16:X16" si="0">D6*COS(RADIANS(D10-12))*D13/1000</f>
+        <v>44.185666386660522</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="0"/>
-        <v>20.758112821237887</v>
+        <v>41.376763734939175</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.865492956682836</v>
       </c>
       <c r="G16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29.094426649018608</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.781100465532006</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="0"/>
@@ -8016,9 +8061,15 @@
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
+      <c r="F17" s="37">
+        <v>50.58</v>
+      </c>
+      <c r="G17" s="37">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H17" s="37">
+        <v>28.8</v>
+      </c>
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
       <c r="K17" s="37"/>
@@ -8042,6 +8093,11 @@
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D541CE-E7A5-4DC6-B614-B6F65C853A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8126D7CE-AF2D-48BF-9724-9E75033E0C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32505" yWindow="2760" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
@@ -1325,22 +1325,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>43.460736823868544</c:v>
+                  <c:v>46.079253454685158</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.185666386660522</c:v>
+                  <c:v>46.778257041650242</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41.376763734939175</c:v>
+                  <c:v>43.708827289351646</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.865492956682836</c:v>
+                  <c:v>46.473685245945447</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.094426649018608</c:v>
+                  <c:v>30.464076188718234</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.781100465532006</c:v>
+                  <c:v>26.140251495852954</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5155,24 +5155,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>0.17953321364452424</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>19.314</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
@@ -5457,7 +5457,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>14</v>
@@ -5505,7 +5505,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>27</v>
@@ -5567,7 +5567,7 @@
         <v>0.22800718132854578</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>17</v>
@@ -5626,7 +5626,7 @@
         <v>366.05</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>18</v>
@@ -5674,13 +5674,13 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -5745,22 +5745,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>6.1297215268519301</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>2.7479725044346299</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>1.5877091527759399</v>
       </c>
@@ -5804,12 +5804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C24">
         <v>0.39396830053809201</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C25">
         <v>0.87997523971335201</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>1.3017605698980601</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>0.32710826122173697</v>
       </c>
@@ -5845,37 +5845,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C28">
         <v>5.7663175704745298</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>0.99793195771798704</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C30">
         <v>1.17473937755851</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C31">
         <v>5.6669972560913404</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C32">
         <v>3.0532323371378101</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33">
         <v>9.8822570388584001</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>5.8339811315985299</v>
       </c>
@@ -5890,29 +5890,29 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>7</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="W6" s="36"/>
       <c r="X6" s="36"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="W7" s="37"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
         <v>10</v>
       </c>
@@ -6080,7 +6080,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
@@ -6137,7 +6137,7 @@
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>14</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="W13" s="37"/>
       <c r="X13" s="37"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
@@ -6248,7 +6248,7 @@
       <c r="W14" s="37"/>
       <c r="X14" s="37"/>
     </row>
-    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
         <v>19</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>20</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -6395,7 +6395,7 @@
       <c r="W17" s="36"/>
       <c r="X17" s="36"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -6412,24 +6412,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>462.31</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>35</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -6599,7 +6599,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -6608,7 +6608,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>36</v>
@@ -6618,7 +6618,7 @@
         <v>0.28366247755834828</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>15</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>17</v>
@@ -6677,7 +6677,7 @@
         <v>240.61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
@@ -6686,13 +6686,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>20</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>37</v>
       </c>
@@ -6768,12 +6768,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>31</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>32</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>18.260899999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>2.018E-2</v>
       </c>
@@ -6813,12 +6813,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>32</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>3.619E-2</v>
       </c>
@@ -6852,19 +6852,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{411EFBF4-5987-49CA-839E-BE22E507CBB9}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -6887,12 +6887,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
         <v>7</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
@@ -7015,7 +7015,7 @@
       <c r="W6" s="36"/>
       <c r="X6" s="36"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
@@ -7048,7 +7048,7 @@
       <c r="W7" s="37"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
         <v>10</v>
       </c>
@@ -7081,7 +7081,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
@@ -7144,7 +7144,7 @@
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>14</v>
       </c>
@@ -7171,7 +7171,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
@@ -7201,7 +7201,7 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>292.89999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
@@ -7299,7 +7299,7 @@
       <c r="W14" s="37"/>
       <c r="X14" s="37"/>
     </row>
-    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>58</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -7446,7 +7446,7 @@
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -7463,19 +7463,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2ABF78-C1E8-448F-AF95-D36F16313176}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -7498,12 +7498,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
         <v>7</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
@@ -7632,7 +7632,7 @@
       <c r="W6" s="36"/>
       <c r="X6" s="36"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
@@ -7671,7 +7671,7 @@
       <c r="W7" s="37"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
         <v>10</v>
       </c>
@@ -7710,7 +7710,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
@@ -7740,7 +7740,7 @@
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
@@ -7779,7 +7779,7 @@
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>14</v>
       </c>
@@ -7806,7 +7806,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
@@ -7836,78 +7836,78 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="D13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="E13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="F13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="G13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="H13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="I13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="J13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="K13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="L13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="M13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="N13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="O13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="P13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="Q13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="R13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="S13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="T13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="U13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="V13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="W13" s="37">
-        <v>250.9</v>
+        <v>263.2</v>
       </c>
       <c r="X13" s="37">
-        <v>250.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+        <v>263.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
@@ -7934,7 +7934,7 @@
       <c r="W14" s="37"/>
       <c r="X14" s="37"/>
     </row>
-    <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
         <v>19</v>
       </c>
@@ -7961,33 +7961,33 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="36">
-        <f>C6*COS(RADIANS(C10-12))*C13/1000</f>
-        <v>43.460736823868544</v>
+        <f>C6*COS(RADIANS(C10-14.3))*C13/1000</f>
+        <v>46.079253454685158</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:X16" si="0">D6*COS(RADIANS(D10-12))*D13/1000</f>
-        <v>44.185666386660522</v>
+        <f t="shared" ref="D16:X16" si="0">D6*COS(RADIANS(D10-14.3))*D13/1000</f>
+        <v>46.778257041650242</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="0"/>
-        <v>41.376763734939175</v>
+        <v>43.708827289351646</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="0"/>
-        <v>43.865492956682836</v>
+        <v>46.473685245945447</v>
       </c>
       <c r="G16" s="36">
         <f t="shared" si="0"/>
-        <v>29.094426649018608</v>
+        <v>30.464076188718234</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="0"/>
-        <v>24.781100465532006</v>
+        <v>26.140251495852954</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="0"/>
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -8087,7 +8087,7 @@
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>59</v>
       </c>
@@ -8109,24 +8109,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>4.8666</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>-120</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -8514,7 +8514,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -8573,7 +8573,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -8596,7 +8596,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>17</v>
@@ -8653,7 +8653,7 @@
         <v>366.43</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>18</v>
@@ -8710,13 +8710,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>-1.0937153129886135</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -8845,22 +8845,22 @@
         <v>-0.77272430551831095</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="M19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="R20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -8878,24 +8878,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>606.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -9129,7 +9129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -9157,7 +9157,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -9180,7 +9180,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>17</v>
@@ -9234,7 +9234,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>18</v>
@@ -9258,13 +9258,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -9337,12 +9337,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -9360,24 +9360,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>50.45</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -9569,7 +9569,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -9591,7 +9591,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -9614,7 +9614,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>17</v>
@@ -9668,7 +9668,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>18</v>
@@ -9686,13 +9686,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -9791,24 +9791,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9844,7 +9844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>78.14</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -10036,7 +10036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -10070,7 +10070,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
@@ -10093,7 +10093,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>17</v>
@@ -10147,7 +10147,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>18</v>
@@ -10177,13 +10177,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>-22.190799999999999</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -10297,24 +10297,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -10355,7 +10355,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="27" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" s="27" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23"/>
       <c r="B5" s="24" t="s">
         <v>7</v>
@@ -10465,7 +10465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
         <v>10</v>
@@ -10679,7 +10679,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
@@ -10709,7 +10709,7 @@
       <c r="W9" s="21"/>
       <c r="X9" s="21"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="3" t="s">
         <v>13</v>
@@ -10781,7 +10781,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="34" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" s="34" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
       <c r="B11" s="28" t="s">
         <v>14</v>
@@ -10853,7 +10853,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
@@ -10883,7 +10883,7 @@
       <c r="W12" s="21"/>
       <c r="X12" s="21"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="3" t="s">
         <v>17</v>
@@ -10973,7 +10973,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="3" t="s">
         <v>18</v>
@@ -11045,7 +11045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" s="32" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33"/>
       <c r="B15" s="28" t="s">
         <v>19</v>
@@ -11073,7 +11073,7 @@
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>20</v>
       </c>
@@ -11190,7 +11190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>-23.6068</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="K18" t="s">
         <v>48</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="U19" t="s">
         <v>50</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
         <v>52</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8126D7CE-AF2D-48BF-9724-9E75033E0C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF60C62-5EE5-4E66-93DF-91FD720B36C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32505" yWindow="2760" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
@@ -1315,6 +1315,15 @@
                 <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-22</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-86.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1325,31 +1334,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>46.079253454685158</c:v>
+                  <c:v>44.8113882594823</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46.778257041650242</c:v>
+                  <c:v>45.585747457333838</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.708827289351646</c:v>
+                  <c:v>42.724833518295966</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.473685245945447</c:v>
+                  <c:v>45.242138509683038</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.464076188718234</c:v>
+                  <c:v>30.146746944099203</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26.140251495852954</c:v>
+                  <c:v>25.602991386762568</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>31.494527360331841</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>43.120392476105614</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>35.729549720172791</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -7615,9 +7624,15 @@
       <c r="H6" s="36">
         <v>100</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
+      <c r="I6" s="36">
+        <v>126</v>
+      </c>
+      <c r="J6" s="36">
+        <v>173.4</v>
+      </c>
+      <c r="K6" s="36">
+        <v>140</v>
+      </c>
       <c r="L6" s="36"/>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
@@ -7654,9 +7669,15 @@
       <c r="H7" s="37">
         <v>5</v>
       </c>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
+      <c r="I7" s="37">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="37">
+        <v>-22</v>
+      </c>
+      <c r="K7" s="37">
+        <v>-86.5</v>
+      </c>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
       <c r="N7" s="37"/>
@@ -7693,9 +7714,15 @@
       <c r="H8" s="38">
         <v>480</v>
       </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
+      <c r="I8" s="38">
+        <v>488</v>
+      </c>
+      <c r="J8" s="38">
+        <v>435</v>
+      </c>
+      <c r="K8" s="38">
+        <v>350</v>
+      </c>
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
       <c r="N8" s="38"/>
@@ -7762,9 +7789,15 @@
       <c r="H10" s="37">
         <v>21</v>
       </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
+      <c r="I10" s="37">
+        <v>27</v>
+      </c>
+      <c r="J10" s="37">
+        <v>28</v>
+      </c>
+      <c r="K10" s="37">
+        <v>22</v>
+      </c>
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
@@ -7841,70 +7874,70 @@
         <v>17</v>
       </c>
       <c r="C13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="D13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="E13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="F13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="G13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="H13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="I13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="J13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="K13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="L13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="M13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="N13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="O13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="P13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="Q13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="R13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="S13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="T13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="U13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="V13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="W13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="X13" s="37">
-        <v>263.2</v>
+        <v>259.89999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -7966,40 +7999,40 @@
         <v>58</v>
       </c>
       <c r="C16" s="36">
-        <f>C6*COS(RADIANS(C10-14.3))*C13/1000</f>
-        <v>46.079253454685158</v>
+        <f>C6*COS(RADIANS(C10-11.1))*C13/1000</f>
+        <v>44.8113882594823</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:X16" si="0">D6*COS(RADIANS(D10-14.3))*D13/1000</f>
-        <v>46.778257041650242</v>
+        <f t="shared" ref="D16:X16" si="0">D6*COS(RADIANS(D10-11.1))*D13/1000</f>
+        <v>45.585747457333838</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="0"/>
-        <v>43.708827289351646</v>
+        <v>42.724833518295966</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="0"/>
-        <v>46.473685245945447</v>
+        <v>45.242138509683038</v>
       </c>
       <c r="G16" s="36">
         <f t="shared" si="0"/>
-        <v>30.464076188718234</v>
+        <v>30.146746944099203</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="0"/>
-        <v>26.140251495852954</v>
+        <v>25.602991386762568</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31.494527360331841</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.120392476105614</v>
       </c>
       <c r="K16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35.729549720172791</v>
       </c>
       <c r="L16" s="36">
         <f t="shared" si="0"/>
@@ -8070,9 +8103,15 @@
       <c r="H17" s="37">
         <v>28.8</v>
       </c>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
+      <c r="I17" s="37">
+        <v>36.86</v>
+      </c>
+      <c r="J17" s="37">
+        <v>49.95</v>
+      </c>
+      <c r="K17" s="37">
+        <v>39.71</v>
+      </c>
       <c r="L17" s="37"/>
       <c r="M17" s="37"/>
       <c r="N17" s="37"/>
@@ -8102,7 +8141,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF60C62-5EE5-4E66-93DF-91FD720B36C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3DDD7F-F918-4298-B1CC-C0BAB550788C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7260" yWindow="4080" windowWidth="21600" windowHeight="11295" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="FlxTest20mm_39cm (2)" sheetId="6" r:id="rId7"/>
     <sheet name="FlxTest20mm_42cm (2)" sheetId="7" r:id="rId8"/>
     <sheet name="FlxTest20mm_42cm (3)" sheetId="8" r:id="rId9"/>
-    <sheet name="FlxTest20mm_51cm" sheetId="9" r:id="rId10"/>
+    <sheet name="FlxTest20mm_56cm" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="60">
   <si>
     <t>Flexor Test 20mm</t>
   </si>
@@ -4302,7 +4302,14 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -4348,63 +4355,108 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest20mm_51cm!$C$7:$X$7</c:f>
+              <c:f>FlxTest20mm_56cm!$C$7:$X$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>-61.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-83</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-52</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-42</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-114</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-119</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-62</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-78</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-87</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-22.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-14</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest20mm_51cm!$C$16:$X$16</c:f>
+              <c:f>FlxTest20mm_56cm!$C$16:$X$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-26.939978516292122</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-14.116158452839818</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-23.436268308059354</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>-21.636104000084657</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>-21.103040568198516</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>-24.771771246473737</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>-30.102405565335182</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>-5.0191098324557109</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-2.7856059570129195</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>-23.498977136149122</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>-17.383088404549934</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>-19.91977312840131</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>-7.2446005347718438</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-30.761488976351835</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>-34.947591111946373</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -4433,7 +4485,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5E1D-4E97-A3D3-CC32CBB65176}"/>
+              <c16:uniqueId val="{00000000-65DD-4B8B-99EA-EC89646EDCAB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4845,11 +4897,13 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4694316A-082E-4A38-844D-CB3C6BD01D95}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5897,7 +5951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77502660-85AA-4B65-93D8-6FCA676E136E}">
   <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5915,6 +5969,24 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -5925,19 +5997,44 @@
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="C3">
+        <f>0.255*C2</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>0.255*D2</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" t="e">
+        <f>1-F3/C2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J3" t="e">
+        <f>1-G3/D2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4">
+        <v>0.92</v>
+      </c>
+      <c r="D4">
+        <v>0.85</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
         <v>7</v>
       </c>
@@ -6012,21 +6109,51 @@
       <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
+      <c r="C6" s="36">
+        <v>84</v>
+      </c>
+      <c r="D6" s="36">
+        <v>51</v>
+      </c>
+      <c r="E6" s="36">
+        <v>77.8</v>
+      </c>
+      <c r="F6" s="36">
+        <v>69</v>
+      </c>
+      <c r="G6" s="36">
+        <v>67.3</v>
+      </c>
+      <c r="H6" s="36">
+        <v>79</v>
+      </c>
+      <c r="I6" s="36">
+        <v>96</v>
+      </c>
+      <c r="J6" s="36">
+        <v>20</v>
+      </c>
+      <c r="K6" s="36">
+        <v>11.1</v>
+      </c>
+      <c r="L6" s="36">
+        <v>77</v>
+      </c>
+      <c r="M6" s="36">
+        <v>60</v>
+      </c>
+      <c r="N6" s="36">
+        <v>69.5</v>
+      </c>
+      <c r="O6" s="36">
+        <v>28</v>
+      </c>
+      <c r="P6" s="36">
+        <v>93.7</v>
+      </c>
+      <c r="Q6" s="36">
+        <v>106</v>
+      </c>
       <c r="R6" s="36"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
@@ -6039,21 +6166,51 @@
       <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
+      <c r="C7" s="37">
+        <v>-61.5</v>
+      </c>
+      <c r="D7" s="37">
+        <v>-83</v>
+      </c>
+      <c r="E7" s="37">
+        <v>5</v>
+      </c>
+      <c r="F7" s="37">
+        <v>-5</v>
+      </c>
+      <c r="G7" s="37">
+        <v>-52</v>
+      </c>
+      <c r="H7" s="37">
+        <v>-45</v>
+      </c>
+      <c r="I7" s="37">
+        <v>-42</v>
+      </c>
+      <c r="J7" s="37">
+        <v>-114</v>
+      </c>
+      <c r="K7" s="37">
+        <v>-119</v>
+      </c>
+      <c r="L7" s="37">
+        <v>-62</v>
+      </c>
+      <c r="M7" s="37">
+        <v>-78</v>
+      </c>
+      <c r="N7" s="37">
+        <v>-87</v>
+      </c>
+      <c r="O7" s="37">
+        <v>-105</v>
+      </c>
+      <c r="P7" s="37">
+        <v>-22.5</v>
+      </c>
+      <c r="Q7" s="37">
+        <v>-14</v>
+      </c>
       <c r="R7" s="37"/>
       <c r="S7" s="37"/>
       <c r="T7" s="37"/>
@@ -6066,21 +6223,51 @@
       <c r="B8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
+      <c r="C8" s="38">
+        <v>517</v>
+      </c>
+      <c r="D8" s="38">
+        <v>628</v>
+      </c>
+      <c r="E8" s="38">
+        <v>226.5</v>
+      </c>
+      <c r="F8" s="38">
+        <v>242.5</v>
+      </c>
+      <c r="G8" s="38">
+        <v>406.7</v>
+      </c>
+      <c r="H8" s="38">
+        <v>410.3</v>
+      </c>
+      <c r="I8" s="38">
+        <v>412</v>
+      </c>
+      <c r="J8" s="38">
+        <v>634</v>
+      </c>
+      <c r="K8" s="38">
+        <v>633</v>
+      </c>
+      <c r="L8" s="38">
+        <v>400</v>
+      </c>
+      <c r="M8" s="38">
+        <v>489</v>
+      </c>
+      <c r="N8" s="38">
+        <v>635</v>
+      </c>
+      <c r="O8" s="38">
+        <v>638</v>
+      </c>
+      <c r="P8" s="38">
+        <v>275.3</v>
+      </c>
+      <c r="Q8" s="38">
+        <v>273.7</v>
+      </c>
       <c r="R8" s="38"/>
       <c r="S8" s="38"/>
       <c r="T8" s="38"/>
@@ -6123,21 +6310,51 @@
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
+      <c r="C10" s="37">
+        <v>35</v>
+      </c>
+      <c r="D10" s="37">
+        <v>38</v>
+      </c>
+      <c r="E10" s="37">
+        <v>30</v>
+      </c>
+      <c r="F10" s="37">
+        <v>25</v>
+      </c>
+      <c r="G10" s="37">
+        <v>25</v>
+      </c>
+      <c r="H10" s="37">
+        <v>25</v>
+      </c>
+      <c r="I10" s="37">
+        <v>25</v>
+      </c>
+      <c r="J10" s="37">
+        <v>45</v>
+      </c>
+      <c r="K10" s="37">
+        <v>45</v>
+      </c>
+      <c r="L10" s="37">
+        <v>28.5</v>
+      </c>
+      <c r="M10" s="37">
+        <v>34</v>
+      </c>
+      <c r="N10" s="37">
+        <v>35</v>
+      </c>
+      <c r="O10" s="37">
+        <v>43</v>
+      </c>
+      <c r="P10" s="37">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="37">
+        <v>16</v>
+      </c>
       <c r="R10" s="37"/>
       <c r="S10" s="37"/>
       <c r="T10" s="37"/>
@@ -6207,28 +6424,72 @@
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
+      <c r="C13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="D13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="E13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="F13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="G13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="H13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="I13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="J13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="K13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="L13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="M13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="N13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="O13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="P13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="Q13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="R13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="S13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="T13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="U13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="V13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="W13" s="37">
+        <v>338.6</v>
+      </c>
+      <c r="X13" s="37">
+        <v>338.6</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
@@ -6289,64 +6550,64 @@
         <v>20</v>
       </c>
       <c r="C16" s="36">
-        <f t="shared" ref="C16:X16" si="0">-C6*COS(RADIANS(C10-2.83))*C13/1000</f>
-        <v>0</v>
+        <f>-C6*COS(RADIANS(C10-16.294))*C13/1000</f>
+        <v>-26.939978516292122</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="C16:X16" si="0">-D6*COS(RADIANS(D10-2.83))*D13/1000</f>
+        <v>-14.116158452839818</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>-E6*COS(RADIANS(E10-2.83))*E13/1000</f>
+        <v>-23.436268308059354</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-21.636104000084657</v>
       </c>
       <c r="G16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-21.103040568198516</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-24.771771246473737</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-30.102405565335182</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5.0191098324557109</v>
       </c>
       <c r="K16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.7856059570129195</v>
       </c>
       <c r="L16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-23.498977136149122</v>
       </c>
       <c r="M16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-17.383088404549934</v>
       </c>
       <c r="N16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-19.91977312840131</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7.2446005347718438</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-30.761488976351835</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-34.947591111946373</v>
       </c>
       <c r="R16" s="36">
         <f t="shared" si="0"/>
@@ -6383,19 +6644,45 @@
       </c>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
+      <c r="E17" s="36">
+        <v>-27.78</v>
+      </c>
+      <c r="F17" s="36">
+        <v>-24.51</v>
+      </c>
+      <c r="G17" s="36">
+        <v>-23.68</v>
+      </c>
+      <c r="H17" s="36">
+        <v>-27.72</v>
+      </c>
+      <c r="I17" s="36">
+        <v>-33.700000000000003</v>
+      </c>
+      <c r="J17" s="36">
+        <v>-6.3</v>
+      </c>
+      <c r="K17" s="36">
+        <v>-3.5</v>
+      </c>
+      <c r="L17" s="36">
+        <v>-27</v>
+      </c>
+      <c r="M17" s="36">
+        <v>-20.170000000000002</v>
+      </c>
+      <c r="N17" s="36">
+        <v>-23.34</v>
+      </c>
+      <c r="O17" s="36">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="P17" s="36">
+        <v>-33.340000000000003</v>
+      </c>
+      <c r="Q17" s="36">
+        <v>-37.78</v>
+      </c>
       <c r="R17" s="36"/>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
@@ -6905,16 +7192,38 @@
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="C3">
+        <f>0.255*C2</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>0.255*D2</f>
+        <v>0</v>
+      </c>
       <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H3" t="s">
         <v>57</v>
+      </c>
+      <c r="I3" t="e">
+        <f>1-F3/C2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J3" t="e">
+        <f>1-G3/D2</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.92</v>
+      </c>
+      <c r="D4">
+        <v>0.85</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>5</v>

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -6701,7 +6701,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3DDD7F-F918-4298-B1CC-C0BAB550788C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9B12B5-6091-4075-9E61-955A83B32721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="4080" windowWidth="21600" windowHeight="11295" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="62">
   <si>
     <t>Flexor Test 20mm</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>Torque actual*</t>
+  </si>
+  <si>
+    <t>*actual torque is calculated in the scripts, this is just the output from the live reading. Both torque values given as a sanity check.</t>
   </si>
 </sst>
 </file>
@@ -507,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -552,6 +558,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5992,6 +5999,12 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="D2">
+        <v>0.56000000000000005</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -5999,25 +6012,31 @@
       </c>
       <c r="C3">
         <f>0.255*C2</f>
-        <v>0</v>
+        <v>0.14305500000000002</v>
       </c>
       <c r="D3">
         <f>0.255*D2</f>
-        <v>0</v>
+        <v>0.14280000000000001</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="F3">
+        <v>0.43</v>
+      </c>
+      <c r="G3">
+        <v>0.42799999999999999</v>
+      </c>
       <c r="H3" t="s">
         <v>57</v>
       </c>
-      <c r="I3" t="e">
+      <c r="I3">
         <f>1-F3/C2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J3" t="e">
+        <v>0.23351158645276304</v>
+      </c>
+      <c r="J3">
         <f>1-G3/D2</f>
-        <v>#DIV/0!</v>
+        <v>0.23571428571428577</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6025,10 +6044,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.92</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D4">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>5</v>
@@ -6554,7 +6573,7 @@
         <v>-26.939978516292122</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="C16:X16" si="0">-D6*COS(RADIANS(D10-2.83))*D13/1000</f>
+        <f t="shared" ref="D16:X16" si="0">-D6*COS(RADIANS(D10-2.83))*D13/1000</f>
         <v>-14.116158452839818</v>
       </c>
       <c r="E16" s="36">
@@ -7188,6 +7207,12 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="D2">
+        <v>0.82599999999999996</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -7195,25 +7220,31 @@
       </c>
       <c r="C3">
         <f>0.255*C2</f>
-        <v>0</v>
+        <v>0.21113999999999999</v>
       </c>
       <c r="D3">
         <f>0.255*D2</f>
-        <v>0</v>
+        <v>0.21062999999999998</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="F3">
+        <v>0.622</v>
+      </c>
+      <c r="G3">
+        <v>0.621</v>
+      </c>
       <c r="H3" t="s">
         <v>57</v>
       </c>
-      <c r="I3" t="e">
+      <c r="I3">
         <f>1-F3/C2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J3" t="e">
+        <v>0.24879227053140096</v>
+      </c>
+      <c r="J3">
         <f>1-G3/D2</f>
-        <v>#DIV/0!</v>
+        <v>0.24818401937045997</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7821,21 +7852,55 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="D2">
+        <v>0.82599999999999996</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="C3">
+        <f>0.255*C2</f>
+        <v>0.21113999999999999</v>
+      </c>
+      <c r="D3">
+        <f>0.255*D2</f>
+        <v>0.21062999999999998</v>
+      </c>
       <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="F3">
+        <v>0.622</v>
+      </c>
+      <c r="G3">
+        <v>0.621</v>
+      </c>
       <c r="H3" t="s">
         <v>57</v>
+      </c>
+      <c r="I3">
+        <f>1-F3/C2</f>
+        <v>0.24879227053140096</v>
+      </c>
+      <c r="J3">
+        <f>1-G3/D2</f>
+        <v>0.24818401937045997</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.92</v>
+      </c>
+      <c r="D4">
+        <v>0.85</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>5</v>
@@ -8399,7 +8464,7 @@
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
@@ -8435,6 +8500,11 @@
       <c r="V17" s="37"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B19" s="40" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">

--- a/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
+++ b/Testing_Data/2026_06_Festo/Results_table_20mm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9B12B5-6091-4075-9E61-955A83B32721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91858DA-CC1A-477E-8167-7B0B301BF93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="62">
   <si>
     <t>Flexor Test 20mm</t>
   </si>
@@ -558,7 +558,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6659,7 +6659,7 @@
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -6709,6 +6709,11 @@
       <c r="V17" s="36"/>
       <c r="W17" s="36"/>
       <c r="X17" s="36"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B19" s="40" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
